--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$34</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="275">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -714,17 +714,6 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
-    <t>&lt;valueCodeableReference xmlns="http://hl7.org/fhir"&gt;
-  &lt;concept&gt;
-    &lt;coding&gt;
-      &lt;system value="http://snomed.info/sct"/&gt;
-      &lt;code value="387066007"/&gt;
-      &lt;display value="Tenecteplase (substance)"/&gt;
-    &lt;/coding&gt;
-  &lt;/concept&gt;
-&lt;/valueCodeableReference&gt;</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/medication-codes|5.0.0</t>
   </si>
   <si>
@@ -732,6 +721,59 @@
   </si>
   <si>
     <t>RXC-2 Component Code  if medication: RXO-1 Requested Give Code / RXE-2 Give Code / RXD-2-Dispense Give Code / RXG-4 Give Code / RXA-5 Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item.concept</t>
+  </si>
+  <si>
+    <t>Reference to a concept (by class)</t>
+  </si>
+  <si>
+    <t>A reference to a concept - e.g. the information is identified by its general class to the degree of precision found in the terminology.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="387066007"/&gt;
+    &lt;display value="Tenecteplase (substance)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>CodeableReference.concept</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>A reference to a resource the provides exact details about the information being referenced.</t>
+  </si>
+  <si>
+    <t>CodeableReference.reference</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -1171,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.7734375" customWidth="true" bestFit="true"/>
@@ -1202,7 +1244,7 @@
     <col min="26" max="26" width="51.06640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="33.7734375" customWidth="true" bestFit="true" hidden="true"/>
@@ -3543,7 +3585,7 @@
         <v>78</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>78</v>
@@ -3562,7 +3604,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
@@ -3601,18 +3643,18 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3635,18 +3677,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -3655,7 +3695,7 @@
         <v>78</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>78</v>
@@ -3694,7 +3734,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3703,10 +3743,10 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
@@ -3715,7 +3755,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -3723,21 +3763,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -3749,15 +3789,17 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -3782,63 +3824,63 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>78</v>
+        <v>224</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3858,16 +3900,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3879,7 +3921,7 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>78</v>
@@ -3918,7 +3960,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3933,13 +3975,13 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>134</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -3947,10 +3989,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3970,16 +4012,16 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4030,7 +4072,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4039,10 +4081,10 @@
         <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
@@ -4051,7 +4093,7 @@
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4059,21 +4101,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4085,18 +4127,18 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4105,7 +4147,7 @@
         <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>78</v>
@@ -4144,19 +4186,19 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -4165,7 +4207,7 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4173,46 +4215,42 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4236,13 +4274,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4260,39 +4298,39 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4315,13 +4353,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4372,7 +4410,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4387,24 +4425,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>154</v>
+        <v>257</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4427,13 +4465,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4484,7 +4522,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4493,41 +4531,41 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>255</v>
+        <v>205</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4539,15 +4577,17 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -4596,35 +4636,487 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AI30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
+      <c r="H32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AK32" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN30">
+  <autoFilter ref="A1:AN34">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4634,7 +5126,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI29">
+  <conditionalFormatting sqref="A2:AI33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -751,8 +751,8 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;code value="387066007"/&gt;
-    &lt;display value="Tenecteplase (substance)"/&gt;
+    &lt;code value="127967007"/&gt;
+    &lt;display value="Product containing tenecteplase (medicinal product)"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/tenecteplase-brand-medication-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/tenecteplase-brand-medication-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -526,7 +526,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/tenecteplase-brand-vs</t>
+    <t>http://qualityregistry.org/ValueSet/tenecteplase-brand-vs</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode
--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
+++ b/StructureDefinition-tenecteplase-brand-medication-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
